--- a/doc/presentation/Vulnerability Data.xlsx
+++ b/doc/presentation/Vulnerability Data.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tynan\Documents\ETH\repos\thesis\doc\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1439248E-DC54-4CE1-89DA-2F73F931B6FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E92EF0D-6E38-473C-A941-31EB599F7CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{03F1912C-B5FA-4CD4-A6A8-A41878F5EC45}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{03F1912C-B5FA-4CD4-A6A8-A41878F5EC45}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>

--- a/doc/presentation/Vulnerability Data.xlsx
+++ b/doc/presentation/Vulnerability Data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Tynan\Documents\ETH\repos\thesis\doc\presentation\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\tynan\Documents\ETH\repos\thesis\doc\presentation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9E92EF0D-6E38-473C-A941-31EB599F7CDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E94E274-9BF6-4782-9AE1-318E4E0C888F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="23232" windowHeight="13992" xr2:uid="{03F1912C-B5FA-4CD4-A6A8-A41878F5EC45}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{03F1912C-B5FA-4CD4-A6A8-A41878F5EC45}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="23">
   <si>
     <t>Category</t>
   </si>
@@ -93,6 +93,18 @@
   </si>
   <si>
     <t>Total</t>
+  </si>
+  <si>
+    <t>Counts 2021</t>
+  </si>
+  <si>
+    <t>Counts 2022</t>
+  </si>
+  <si>
+    <t>Counts 2023</t>
+  </si>
+  <si>
+    <t>Counts 2024</t>
   </si>
 </sst>
 </file>
@@ -1266,16 +1278,16 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2021</c:v>
+                  <c:v>Counts 2021</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022</c:v>
+                  <c:v>Counts 2022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023</c:v>
+                  <c:v>Counts 2023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2024</c:v>
+                  <c:v>Counts 2024</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Total</c:v>
@@ -1349,16 +1361,16 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2021</c:v>
+                  <c:v>Counts 2021</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022</c:v>
+                  <c:v>Counts 2022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023</c:v>
+                  <c:v>Counts 2023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2024</c:v>
+                  <c:v>Counts 2024</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Total</c:v>
@@ -1432,16 +1444,16 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2021</c:v>
+                  <c:v>Counts 2021</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022</c:v>
+                  <c:v>Counts 2022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023</c:v>
+                  <c:v>Counts 2023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2024</c:v>
+                  <c:v>Counts 2024</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Total</c:v>
@@ -1515,16 +1527,16 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2021</c:v>
+                  <c:v>Counts 2021</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022</c:v>
+                  <c:v>Counts 2022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023</c:v>
+                  <c:v>Counts 2023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2024</c:v>
+                  <c:v>Counts 2024</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Total</c:v>
@@ -1598,16 +1610,16 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2021</c:v>
+                  <c:v>Counts 2021</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022</c:v>
+                  <c:v>Counts 2022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023</c:v>
+                  <c:v>Counts 2023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2024</c:v>
+                  <c:v>Counts 2024</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Total</c:v>
@@ -1681,16 +1693,16 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2021</c:v>
+                  <c:v>Counts 2021</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022</c:v>
+                  <c:v>Counts 2022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023</c:v>
+                  <c:v>Counts 2023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2024</c:v>
+                  <c:v>Counts 2024</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Total</c:v>
@@ -1766,16 +1778,16 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2021</c:v>
+                  <c:v>Counts 2021</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022</c:v>
+                  <c:v>Counts 2022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023</c:v>
+                  <c:v>Counts 2023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2024</c:v>
+                  <c:v>Counts 2024</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Total</c:v>
@@ -1851,16 +1863,16 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2021</c:v>
+                  <c:v>Counts 2021</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022</c:v>
+                  <c:v>Counts 2022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023</c:v>
+                  <c:v>Counts 2023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2024</c:v>
+                  <c:v>Counts 2024</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Total</c:v>
@@ -1936,16 +1948,16 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2021</c:v>
+                  <c:v>Counts 2021</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022</c:v>
+                  <c:v>Counts 2022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023</c:v>
+                  <c:v>Counts 2023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2024</c:v>
+                  <c:v>Counts 2024</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Total</c:v>
@@ -2021,16 +2033,16 @@
               <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>2021</c:v>
+                  <c:v>Counts 2021</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2022</c:v>
+                  <c:v>Counts 2022</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2023</c:v>
+                  <c:v>Counts 2023</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2024</c:v>
+                  <c:v>Counts 2024</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>Total</c:v>
@@ -3761,13 +3773,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{306C9F8D-DC8D-40B5-94BA-B29760AD03CE}">
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:W29"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="18" max="18" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -3789,8 +3801,23 @@
       <c r="G1" t="s">
         <v>17</v>
       </c>
+      <c r="S1" t="s">
+        <v>1</v>
+      </c>
+      <c r="T1" t="s">
+        <v>2</v>
+      </c>
+      <c r="U1" t="s">
+        <v>3</v>
+      </c>
+      <c r="V1" t="s">
+        <v>4</v>
+      </c>
+      <c r="W1" t="s">
+        <v>5</v>
+      </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -3807,15 +3834,38 @@
         <v>61</v>
       </c>
       <c r="F2">
-        <f>B2+C2+D2+E2</f>
+        <f t="shared" ref="F2:F11" si="0">B2+C2+D2+E2</f>
         <v>524</v>
       </c>
       <c r="G2">
         <f>100*_xlfn.PERCENTOF(F2, F2:F11)</f>
         <v>31.354996604205994</v>
       </c>
+      <c r="R2" t="s">
+        <v>6</v>
+      </c>
+      <c r="S2">
+        <f t="shared" ref="S2:V2" si="1">100*_xlfn.PERCENTOF(B2, B2:B11)</f>
+        <v>13.771657041314972</v>
+      </c>
+      <c r="T2">
+        <f t="shared" si="1"/>
+        <v>44.614212383702281</v>
+      </c>
+      <c r="U2">
+        <f t="shared" si="1"/>
+        <v>43.425936383924224</v>
+      </c>
+      <c r="V2">
+        <f t="shared" si="1"/>
+        <v>19.773672489635029</v>
+      </c>
+      <c r="W2">
+        <f>100*_xlfn.PERCENTOF(F2, F2:F11)</f>
+        <v>31.354996604205994</v>
+      </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -3832,15 +3882,38 @@
         <v>44</v>
       </c>
       <c r="F3">
-        <f>B3+C3+D3+E3</f>
+        <f t="shared" si="0"/>
         <v>422</v>
       </c>
       <c r="G3">
         <f>100*_xlfn.PERCENTOF(F3, F2:F11)</f>
         <v>25.251543066746045</v>
       </c>
+      <c r="R3" t="s">
+        <v>7</v>
+      </c>
+      <c r="S3">
+        <f t="shared" ref="S3:V3" si="2">100*_xlfn.PERCENTOF(B3, B2:B11)</f>
+        <v>47.756552643269664</v>
+      </c>
+      <c r="T3">
+        <f t="shared" si="2"/>
+        <v>12.030798845043311</v>
+      </c>
+      <c r="U3">
+        <f t="shared" si="2"/>
+        <v>22.394541184534912</v>
+      </c>
+      <c r="V3">
+        <f t="shared" si="2"/>
+        <v>14.262976877769532</v>
+      </c>
+      <c r="W3">
+        <f>100*_xlfn.PERCENTOF(F3, F2:F11)</f>
+        <v>25.251543066746045</v>
+      </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -3857,15 +3930,38 @@
         <v>15</v>
       </c>
       <c r="F4">
-        <f>B4+C4+D4+E4</f>
+        <f t="shared" si="0"/>
         <v>60.5</v>
       </c>
       <c r="G4">
         <f>100*_xlfn.PERCENTOF(F4, F2:F11)</f>
         <v>3.6201856766306535</v>
       </c>
+      <c r="R4" t="s">
+        <v>8</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:V4" si="3">100*_xlfn.PERCENTOF(B4, B2:B11)</f>
+        <v>0.88849400266548195</v>
+      </c>
+      <c r="T4">
+        <f t="shared" si="3"/>
+        <v>6.5166827077317944</v>
+      </c>
+      <c r="U4">
+        <f t="shared" si="3"/>
+        <v>3.0183946813938363</v>
+      </c>
+      <c r="V4">
+        <f t="shared" si="3"/>
+        <v>4.8623784810577941</v>
+      </c>
+      <c r="W4">
+        <f>100*_xlfn.PERCENTOF(F4, F2:F11)</f>
+        <v>3.6201856766306535</v>
+      </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>9</v>
       </c>
@@ -3882,15 +3978,38 @@
         <v>31</v>
       </c>
       <c r="F5">
-        <f>B5+C5+D5+E5</f>
+        <f t="shared" si="0"/>
         <v>284</v>
       </c>
       <c r="G5">
         <f>100*_xlfn.PERCENTOF(F5, F2:F11)</f>
         <v>16.993929457241418</v>
       </c>
+      <c r="R5" t="s">
+        <v>9</v>
+      </c>
+      <c r="S5">
+        <f t="shared" ref="S5:V5" si="4">100*_xlfn.PERCENTOF(B5, B2:B11)</f>
+        <v>19.324744557974235</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="4"/>
+        <v>25.816089188322106</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>12.268313866310431</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="4"/>
+        <v>10.048915527519442</v>
+      </c>
+      <c r="W5">
+        <f>100*_xlfn.PERCENTOF(F5, F2:F11)</f>
+        <v>16.993929457241418</v>
+      </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -3907,15 +4026,38 @@
         <v>109</v>
       </c>
       <c r="F6">
-        <f>B6+C6+D6+E6</f>
+        <f t="shared" si="0"/>
         <v>141.5</v>
       </c>
       <c r="G6">
         <f>100*_xlfn.PERCENTOF(F6, F2:F11)</f>
         <v>8.4670458387311989</v>
       </c>
+      <c r="R6" t="s">
+        <v>10</v>
+      </c>
+      <c r="S6">
+        <f t="shared" ref="S6:V6" si="5">100*_xlfn.PERCENTOF(B6, B2:B11)</f>
+        <v>4.4424700133274104</v>
+      </c>
+      <c r="T6">
+        <f t="shared" si="5"/>
+        <v>0.47621912094963109</v>
+      </c>
+      <c r="U6">
+        <f t="shared" si="5"/>
+        <v>2.0641924917919137</v>
+      </c>
+      <c r="V6">
+        <f t="shared" si="5"/>
+        <v>35.333283629019974</v>
+      </c>
+      <c r="W6">
+        <f>100*_xlfn.PERCENTOF(F6, F2:F11)</f>
+        <v>8.4670458387311989</v>
+      </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -3932,15 +4074,38 @@
         <v>32</v>
       </c>
       <c r="F7">
-        <f>B7+C7+D7+E7</f>
+        <f t="shared" si="0"/>
         <v>151.69999999999999</v>
       </c>
       <c r="G7">
         <f>100*_xlfn.PERCENTOF(F7, F2:F11)</f>
         <v>9.077391192477192</v>
       </c>
+      <c r="R7" t="s">
+        <v>11</v>
+      </c>
+      <c r="S7">
+        <f t="shared" ref="S7:V7" si="6">100*_xlfn.PERCENTOF(B7, B2:B11)</f>
+        <v>11.328298533984896</v>
+      </c>
+      <c r="T7">
+        <f t="shared" si="6"/>
+        <v>0.92737407763875523</v>
+      </c>
+      <c r="U7">
+        <f t="shared" si="6"/>
+        <v>12.657784147780603</v>
+      </c>
+      <c r="V7">
+        <f t="shared" si="6"/>
+        <v>10.373074092923295</v>
+      </c>
+      <c r="W7">
+        <f>100*_xlfn.PERCENTOF(F7, F2:F11)</f>
+        <v>9.077391192477192</v>
+      </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -3957,15 +4122,38 @@
         <v>9</v>
       </c>
       <c r="F8">
-        <f>B8+C8+D8+E8</f>
+        <f t="shared" si="0"/>
         <v>15.7</v>
       </c>
       <c r="G8">
         <f>100*_xlfn.PERCENTOF(F8, F2:F11)</f>
         <v>0.93945314253059942</v>
       </c>
+      <c r="R8" t="s">
+        <v>12</v>
+      </c>
+      <c r="S8">
+        <f t="shared" ref="S8:V8" si="7">100*_xlfn.PERCENTOF(B8, B2:B11)</f>
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <f t="shared" si="7"/>
+        <v>1.0777590632017966</v>
+      </c>
+      <c r="U8">
+        <f t="shared" si="7"/>
+        <v>0.46736433776420683</v>
+      </c>
+      <c r="V8">
+        <f t="shared" si="7"/>
+        <v>2.9174270886346765</v>
+      </c>
+      <c r="W8">
+        <f>100*_xlfn.PERCENTOF(F8, F2:F11)</f>
+        <v>0.93945314253059942</v>
+      </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -3982,15 +4170,38 @@
         <v>5</v>
       </c>
       <c r="F9">
-        <f>B9+C9+D9+E9</f>
+        <f t="shared" si="0"/>
         <v>5.6310000000000002</v>
       </c>
       <c r="G9">
         <f>100*_xlfn.PERCENTOF(F9, F2:F11)</f>
         <v>0.33694653793565643</v>
       </c>
+      <c r="R9" t="s">
+        <v>13</v>
+      </c>
+      <c r="S9">
+        <f t="shared" ref="S9:V9" si="8">100*_xlfn.PERCENTOF(B9, B2:B11)</f>
+        <v>4.4424700133274105E-2</v>
+      </c>
+      <c r="T9">
+        <f t="shared" si="8"/>
+        <v>1.9048764837985243E-2</v>
+      </c>
+      <c r="U9">
+        <f t="shared" si="8"/>
+        <v>6.9130974960955591E-2</v>
+      </c>
+      <c r="V9">
+        <f t="shared" si="8"/>
+        <v>1.6207928270192649</v>
+      </c>
+      <c r="W9">
+        <f>100*_xlfn.PERCENTOF(F9, F2:F11)</f>
+        <v>0.33694653793565643</v>
+      </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -4007,15 +4218,38 @@
         <v>9.0999999999999998E-2</v>
       </c>
       <c r="F10">
-        <f>B10+C10+D10+E10</f>
+        <f t="shared" si="0"/>
         <v>11.754</v>
       </c>
       <c r="G10">
         <f>100*_xlfn.PERCENTOF(F10, F2:F11)</f>
         <v>0.70333326352259007</v>
       </c>
+      <c r="R10" t="s">
+        <v>14</v>
+      </c>
+      <c r="S10">
+        <f t="shared" ref="S10:V10" si="9">100*_xlfn.PERCENTOF(B10, B2:B11)</f>
+        <v>2.4433585073300756</v>
+      </c>
+      <c r="T10">
+        <f t="shared" si="9"/>
+        <v>0</v>
+      </c>
+      <c r="U10">
+        <f t="shared" si="9"/>
+        <v>0.12910939830736215</v>
+      </c>
+      <c r="V10">
+        <f t="shared" si="9"/>
+        <v>2.9498429451750616E-2</v>
+      </c>
+      <c r="W10">
+        <f>100*_xlfn.PERCENTOF(F10, F2:F11)</f>
+        <v>0.70333326352259007</v>
+      </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -4032,15 +4266,38 @@
         <v>2.4</v>
       </c>
       <c r="F11">
-        <f>B11+C11+D11+E11</f>
+        <f t="shared" si="0"/>
         <v>54.4</v>
       </c>
       <c r="G11">
         <f>100*_xlfn.PERCENTOF(F11, F2:F11)</f>
         <v>3.2551752199786379</v>
       </c>
+      <c r="R11" t="s">
+        <v>15</v>
+      </c>
+      <c r="S11">
+        <f>100*_xlfn.PERCENTOF(B11, B2:B11)</f>
+        <v>0</v>
+      </c>
+      <c r="T11">
+        <f>100*_xlfn.PERCENTOF(C11, C2:C11)</f>
+        <v>8.521815848572345</v>
+      </c>
+      <c r="U11">
+        <f>100*_xlfn.PERCENTOF(D11, D2:D11)</f>
+        <v>3.5052325332315517</v>
+      </c>
+      <c r="V11">
+        <f>100*_xlfn.PERCENTOF(E11, E2:E11)</f>
+        <v>0.77798055696924706</v>
+      </c>
+      <c r="W11">
+        <f>100*_xlfn.PERCENTOF(F11, F2:F11)</f>
+        <v>3.2551752199786379</v>
+      </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:23" x14ac:dyDescent="0.25">
       <c r="F12">
         <f>SUM(F2:F11)</f>
         <v>1671.1850000000002</v>
@@ -4050,21 +4307,21 @@
         <v>99.999999999999986</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>0</v>
       </c>
-      <c r="B18">
-        <v>2021</v>
-      </c>
-      <c r="C18">
-        <v>2022</v>
-      </c>
-      <c r="D18">
-        <v>2023</v>
-      </c>
-      <c r="E18">
-        <v>2024</v>
+      <c r="B18" t="s">
+        <v>19</v>
+      </c>
+      <c r="C18" t="s">
+        <v>20</v>
+      </c>
+      <c r="D18" t="s">
+        <v>21</v>
+      </c>
+      <c r="E18" t="s">
+        <v>22</v>
       </c>
       <c r="F18" t="s">
         <v>18</v>
@@ -4072,8 +4329,23 @@
       <c r="G18" t="s">
         <v>16</v>
       </c>
+      <c r="S18">
+        <v>2021</v>
+      </c>
+      <c r="T18">
+        <v>2022</v>
+      </c>
+      <c r="U18">
+        <v>2023</v>
+      </c>
+      <c r="V18">
+        <v>2024</v>
+      </c>
+      <c r="W18" t="s">
+        <v>18</v>
+      </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>6</v>
       </c>
@@ -4090,15 +4362,38 @@
         <v>58</v>
       </c>
       <c r="F19">
-        <f>B19+C19+D19+E19</f>
+        <f t="shared" ref="F19:F28" si="10">B19+C19+D19+E19</f>
         <v>151</v>
       </c>
       <c r="G19">
         <f>100*_xlfn.PERCENTOF(F19, F19:F28)</f>
         <v>27.504553734061933</v>
       </c>
+      <c r="R19" t="s">
+        <v>6</v>
+      </c>
+      <c r="S19">
+        <f t="shared" ref="S19" si="11">100*_xlfn.PERCENTOF(B19, B19:B28)</f>
+        <v>17.073170731707318</v>
+      </c>
+      <c r="T19">
+        <f t="shared" ref="T19" si="12">100*_xlfn.PERCENTOF(C19, C19:C28)</f>
+        <v>17.948717948717949</v>
+      </c>
+      <c r="U19">
+        <f t="shared" ref="U19" si="13">100*_xlfn.PERCENTOF(D19, D19:D28)</f>
+        <v>30.516431924882632</v>
+      </c>
+      <c r="V19">
+        <f t="shared" ref="V19" si="14">100*_xlfn.PERCENTOF(E19, E19:E28)</f>
+        <v>32.584269662921351</v>
+      </c>
+      <c r="W19">
+        <f t="shared" ref="W19" si="15">100*_xlfn.PERCENTOF(F19, F19:F28)</f>
+        <v>27.504553734061933</v>
+      </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>7</v>
       </c>
@@ -4115,15 +4410,38 @@
         <v>21</v>
       </c>
       <c r="F20">
-        <f>B20+C20+D20+E20</f>
+        <f t="shared" si="10"/>
         <v>108</v>
       </c>
       <c r="G20">
         <f>100*_xlfn.PERCENTOF(F20, F19:F28)</f>
         <v>19.672131147540984</v>
       </c>
+      <c r="R20" t="s">
+        <v>7</v>
+      </c>
+      <c r="S20">
+        <f>100*_xlfn.PERCENTOF(B20, B19:B28)</f>
+        <v>24.390243902439025</v>
+      </c>
+      <c r="T20">
+        <f t="shared" ref="T20" si="16">100*_xlfn.PERCENTOF(C20, C19:C28)</f>
+        <v>29.914529914529915</v>
+      </c>
+      <c r="U20">
+        <f t="shared" ref="U20" si="17">100*_xlfn.PERCENTOF(D20, D19:D28)</f>
+        <v>19.718309859154928</v>
+      </c>
+      <c r="V20">
+        <f t="shared" ref="V20" si="18">100*_xlfn.PERCENTOF(E20, E19:E28)</f>
+        <v>11.797752808988763</v>
+      </c>
+      <c r="W20">
+        <f>100*_xlfn.PERCENTOF(F20, F19:F28)</f>
+        <v>19.672131147540984</v>
+      </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>8</v>
       </c>
@@ -4140,15 +4458,38 @@
         <v>35</v>
       </c>
       <c r="F21">
-        <f>B21+C21+D21+E21</f>
+        <f t="shared" si="10"/>
         <v>76</v>
       </c>
       <c r="G21">
         <f>100*_xlfn.PERCENTOF(F21, F19:F28)</f>
         <v>13.843351548269581</v>
       </c>
+      <c r="R21" t="s">
+        <v>8</v>
+      </c>
+      <c r="S21">
+        <f t="shared" ref="S21" si="19">100*_xlfn.PERCENTOF(B21, B19:B28)</f>
+        <v>7.3170731707317067</v>
+      </c>
+      <c r="T21">
+        <f t="shared" ref="T21" si="20">100*_xlfn.PERCENTOF(C21, C19:C28)</f>
+        <v>13.675213675213676</v>
+      </c>
+      <c r="U21">
+        <f t="shared" ref="U21" si="21">100*_xlfn.PERCENTOF(D21, D19:D28)</f>
+        <v>10.328638497652582</v>
+      </c>
+      <c r="V21">
+        <f t="shared" ref="V21" si="22">100*_xlfn.PERCENTOF(E21, E19:E28)</f>
+        <v>19.662921348314608</v>
+      </c>
+      <c r="W21">
+        <f>100*_xlfn.PERCENTOF(F21, F19:F28)</f>
+        <v>13.843351548269581</v>
+      </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>9</v>
       </c>
@@ -4165,15 +4506,38 @@
         <v>15</v>
       </c>
       <c r="F22">
-        <f>B22+C22+D22+E22</f>
+        <f t="shared" si="10"/>
         <v>54</v>
       </c>
       <c r="G22">
         <f>100*_xlfn.PERCENTOF(F22, F19:F28)</f>
         <v>9.8360655737704921</v>
       </c>
+      <c r="R22" t="s">
+        <v>9</v>
+      </c>
+      <c r="S22">
+        <f t="shared" ref="S22" si="23">100*_xlfn.PERCENTOF(B22, B19:B28)</f>
+        <v>21.951219512195124</v>
+      </c>
+      <c r="T22">
+        <f t="shared" ref="T22" si="24">100*_xlfn.PERCENTOF(C22, C19:C28)</f>
+        <v>11.111111111111111</v>
+      </c>
+      <c r="U22">
+        <f t="shared" ref="U22" si="25">100*_xlfn.PERCENTOF(D22, D19:D28)</f>
+        <v>7.981220657276995</v>
+      </c>
+      <c r="V22">
+        <f t="shared" ref="V22" si="26">100*_xlfn.PERCENTOF(E22, E19:E28)</f>
+        <v>8.4269662921348321</v>
+      </c>
+      <c r="W22">
+        <f>100*_xlfn.PERCENTOF(F22, F19:F28)</f>
+        <v>9.8360655737704921</v>
+      </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>10</v>
       </c>
@@ -4190,15 +4554,38 @@
         <v>18</v>
       </c>
       <c r="F23">
-        <f>B23+C23+D23+E23</f>
+        <f t="shared" si="10"/>
         <v>38</v>
       </c>
       <c r="G23">
         <f>100*_xlfn.PERCENTOF(F23, F19:F28)</f>
         <v>6.9216757741347905</v>
       </c>
+      <c r="R23" t="s">
+        <v>10</v>
+      </c>
+      <c r="S23">
+        <f t="shared" ref="S23" si="27">100*_xlfn.PERCENTOF(B23, B19:B28)</f>
+        <v>4.8780487804878048</v>
+      </c>
+      <c r="T23">
+        <f t="shared" ref="T23" si="28">100*_xlfn.PERCENTOF(C23, C19:C28)</f>
+        <v>8.5470085470085468</v>
+      </c>
+      <c r="U23">
+        <f t="shared" ref="U23" si="29">100*_xlfn.PERCENTOF(D23, D19:D28)</f>
+        <v>3.755868544600939</v>
+      </c>
+      <c r="V23">
+        <f t="shared" ref="V23" si="30">100*_xlfn.PERCENTOF(E23, E19:E28)</f>
+        <v>10.112359550561797</v>
+      </c>
+      <c r="W23">
+        <f>100*_xlfn.PERCENTOF(F23, F19:F28)</f>
+        <v>6.9216757741347905</v>
+      </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>11</v>
       </c>
@@ -4215,15 +4602,38 @@
         <v>12</v>
       </c>
       <c r="F24">
-        <f>B24+C24+D24+E24</f>
+        <f t="shared" si="10"/>
         <v>40</v>
       </c>
       <c r="G24">
         <f>100*_xlfn.PERCENTOF(F24, F19:F28)</f>
         <v>7.2859744990892539</v>
       </c>
+      <c r="R24" t="s">
+        <v>11</v>
+      </c>
+      <c r="S24">
+        <f t="shared" ref="S24" si="31">100*_xlfn.PERCENTOF(B24, B19:B28)</f>
+        <v>12.195121951219512</v>
+      </c>
+      <c r="T24">
+        <f t="shared" ref="T24" si="32">100*_xlfn.PERCENTOF(C24, C19:C28)</f>
+        <v>4.2735042735042734</v>
+      </c>
+      <c r="U24">
+        <f t="shared" ref="U24" si="33">100*_xlfn.PERCENTOF(D24, D19:D28)</f>
+        <v>8.4507042253521121</v>
+      </c>
+      <c r="V24">
+        <f t="shared" ref="V24" si="34">100*_xlfn.PERCENTOF(E24, E19:E28)</f>
+        <v>6.7415730337078648</v>
+      </c>
+      <c r="W24">
+        <f>100*_xlfn.PERCENTOF(F24, F19:F28)</f>
+        <v>7.2859744990892539</v>
+      </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>12</v>
       </c>
@@ -4240,15 +4650,38 @@
         <v>9</v>
       </c>
       <c r="F25">
-        <f>B25+C25+D25+E25</f>
+        <f t="shared" si="10"/>
         <v>26</v>
       </c>
       <c r="G25">
         <f>100*_xlfn.PERCENTOF(F25, F19:F28)</f>
         <v>4.7358834244080148</v>
       </c>
+      <c r="R25" t="s">
+        <v>12</v>
+      </c>
+      <c r="S25">
+        <f t="shared" ref="S25" si="35">100*_xlfn.PERCENTOF(B25, B19:B28)</f>
+        <v>0</v>
+      </c>
+      <c r="T25">
+        <f t="shared" ref="T25" si="36">100*_xlfn.PERCENTOF(C25, C19:C28)</f>
+        <v>6.8376068376068382</v>
+      </c>
+      <c r="U25">
+        <f t="shared" ref="U25" si="37">100*_xlfn.PERCENTOF(D25, D19:D28)</f>
+        <v>4.225352112676056</v>
+      </c>
+      <c r="V25">
+        <f t="shared" ref="V25" si="38">100*_xlfn.PERCENTOF(E25, E19:E28)</f>
+        <v>5.0561797752808983</v>
+      </c>
+      <c r="W25">
+        <f>100*_xlfn.PERCENTOF(F25, F19:F28)</f>
+        <v>4.7358834244080148</v>
+      </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>13</v>
       </c>
@@ -4265,15 +4698,38 @@
         <v>3</v>
       </c>
       <c r="F26">
-        <f>B26+C26+D26+E26</f>
+        <f t="shared" si="10"/>
         <v>28</v>
       </c>
       <c r="G26">
         <f>100*_xlfn.PERCENTOF(F26, F19:F28)</f>
         <v>5.1001821493624773</v>
       </c>
+      <c r="R26" t="s">
+        <v>13</v>
+      </c>
+      <c r="S26">
+        <f t="shared" ref="S26" si="39">100*_xlfn.PERCENTOF(B26, B19:B28)</f>
+        <v>7.3170731707317067</v>
+      </c>
+      <c r="T26">
+        <f t="shared" ref="T26" si="40">100*_xlfn.PERCENTOF(C26, C19:C28)</f>
+        <v>3.4188034188034191</v>
+      </c>
+      <c r="U26">
+        <f t="shared" ref="U26" si="41">100*_xlfn.PERCENTOF(D26, D19:D28)</f>
+        <v>8.4507042253521121</v>
+      </c>
+      <c r="V26">
+        <f t="shared" ref="V26" si="42">100*_xlfn.PERCENTOF(E26, E19:E28)</f>
+        <v>1.6853932584269662</v>
+      </c>
+      <c r="W26">
+        <f>100*_xlfn.PERCENTOF(F26, F19:F28)</f>
+        <v>5.1001821493624773</v>
+      </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>14</v>
       </c>
@@ -4290,15 +4746,38 @@
         <v>2</v>
       </c>
       <c r="F27">
-        <f>B27+C27+D27+E27</f>
+        <f t="shared" si="10"/>
         <v>13</v>
       </c>
       <c r="G27">
         <f>100*_xlfn.PERCENTOF(F27, F19:F28)</f>
         <v>2.3679417122040074</v>
       </c>
+      <c r="R27" t="s">
+        <v>14</v>
+      </c>
+      <c r="S27">
+        <f t="shared" ref="S27" si="43">100*_xlfn.PERCENTOF(B27, B19:B28)</f>
+        <v>4.8780487804878048</v>
+      </c>
+      <c r="T27">
+        <f t="shared" ref="T27" si="44">100*_xlfn.PERCENTOF(C27, C19:C28)</f>
+        <v>0</v>
+      </c>
+      <c r="U27">
+        <f t="shared" ref="U27" si="45">100*_xlfn.PERCENTOF(D27, D19:D28)</f>
+        <v>4.225352112676056</v>
+      </c>
+      <c r="V27">
+        <f t="shared" ref="V27" si="46">100*_xlfn.PERCENTOF(E27, E19:E28)</f>
+        <v>1.1235955056179776</v>
+      </c>
+      <c r="W27">
+        <f>100*_xlfn.PERCENTOF(F27, F19:F28)</f>
+        <v>2.3679417122040074</v>
+      </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>15</v>
       </c>
@@ -4315,15 +4794,38 @@
         <v>5</v>
       </c>
       <c r="F28">
-        <f>B28+C28+D28+E28</f>
+        <f t="shared" si="10"/>
         <v>15</v>
       </c>
       <c r="G28">
         <f>100*_xlfn.PERCENTOF(F28, F19:F28)</f>
         <v>2.7322404371584699</v>
       </c>
+      <c r="R28" t="s">
+        <v>15</v>
+      </c>
+      <c r="S28">
+        <f>100*_xlfn.PERCENTOF(B28, B19:B28)</f>
+        <v>0</v>
+      </c>
+      <c r="T28">
+        <f>100*_xlfn.PERCENTOF(C28, C19:C28)</f>
+        <v>4.2735042735042734</v>
+      </c>
+      <c r="U28">
+        <f>100*_xlfn.PERCENTOF(D28, D19:D28)</f>
+        <v>2.3474178403755865</v>
+      </c>
+      <c r="V28">
+        <f>100*_xlfn.PERCENTOF(E28, E19:E28)</f>
+        <v>2.8089887640449436</v>
+      </c>
+      <c r="W28">
+        <f>100*_xlfn.PERCENTOF(F28, F19:F28)</f>
+        <v>2.7322404371584699</v>
+      </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:23" x14ac:dyDescent="0.25">
       <c r="F29">
         <f>SUM(F19:F28)</f>
         <v>549</v>
